--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260530_204558.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
